--- a/data/Carlson Creek Restoration/Lower Stream/Site 3/IS 3/Site3, #10, 22449418 2027-03-11 13_54_45 PDT (Data PDT).xlsx
+++ b/data/Carlson Creek Restoration/Lower Stream/Site 3/IS 3/Site3, #10, 22449418 2027-03-11 13_54_45 PDT (Data PDT).xlsx
@@ -511,10 +511,10 @@
         <v>46444.45833333334</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.470279693603516</v>
+        <v>5.082</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>94.12286343448243</v>
+        <v>95.17700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -525,10 +525,10 @@
         <v>46444.5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.573917388916016</v>
+        <v>6.348</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>94.0514156493785</v>
+        <v>95.211</v>
       </c>
     </row>
     <row r="4">
@@ -539,10 +539,10 @@
         <v>46444.54166666666</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.071414709091187</v>
+        <v>3.72</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>96.35563630806854</v>
+        <v>97.59</v>
       </c>
     </row>
     <row r="5">
@@ -553,10 +553,10 @@
         <v>46444.58333333334</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3.084659337997437</v>
+        <v>3.397</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>96.31900501681011</v>
+        <v>97.372</v>
       </c>
     </row>
     <row r="6">
@@ -567,10 +567,10 @@
         <v>46444.625</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3.233493566513062</v>
+        <v>3.596</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>96.31279788362973</v>
+        <v>97.348</v>
       </c>
     </row>
     <row r="7">
@@ -581,10 +581,10 @@
         <v>46444.66666666666</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3.382022619247437</v>
+        <v>4.248</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>96.24588709205807</v>
+        <v>97.43000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -595,10 +595,10 @@
         <v>46444.70833333334</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3.349063634872437</v>
+        <v>4.02</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>96.23951557505404</v>
+        <v>97.438</v>
       </c>
     </row>
     <row r="9">
@@ -609,10 +609,10 @@
         <v>46444.75</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3.312747716903687</v>
+        <v>3.744</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>96.28893592779113</v>
+        <v>97.44499999999999</v>
       </c>
     </row>
     <row r="10">
@@ -623,10 +623,10 @@
         <v>46444.79166666666</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3.220279455184937</v>
+        <v>3.953</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>96.30743897097929</v>
+        <v>97.43899999999999</v>
       </c>
     </row>
     <row r="11">
@@ -637,10 +637,10 @@
         <v>46444.83333333334</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3.188876867294312</v>
+        <v>3.791</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>96.34777876129887</v>
+        <v>97.629</v>
       </c>
     </row>
     <row r="12">
@@ -651,10 +651,10 @@
         <v>46444.875</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3.134311437606812</v>
+        <v>3.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>96.39158376262064</v>
+        <v>97.58499999999999</v>
       </c>
     </row>
     <row r="13">
@@ -665,10 +665,10 @@
         <v>46444.91666666666</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3.091281652450562</v>
+        <v>3.671</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>96.40798926821924</v>
+        <v>97.467</v>
       </c>
     </row>
     <row r="14">
@@ -679,10 +679,10 @@
         <v>46444.95833333334</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3.031680822372437</v>
+        <v>3.857</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>96.38621169926431</v>
+        <v>97.652</v>
       </c>
     </row>
     <row r="15">
@@ -693,10 +693,10 @@
         <v>46445</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2.968662023544312</v>
+        <v>3.534</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>96.37824237149458</v>
+        <v>97.56399999999999</v>
       </c>
     </row>
     <row r="16">
@@ -707,10 +707,10 @@
         <v>46445.04166666666</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2.928867101669312</v>
+        <v>3.531</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.40880461198445</v>
+        <v>97.548</v>
       </c>
     </row>
     <row r="17">
@@ -721,10 +721,10 @@
         <v>46445.08333333334</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2.892368078231812</v>
+        <v>3.387</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>96.397554183095</v>
+        <v>97.54300000000001</v>
       </c>
     </row>
     <row r="18">
@@ -735,10 +735,10 @@
         <v>46445.125</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2.829257726669312</v>
+        <v>3.535</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>96.3522500013017</v>
+        <v>97.53700000000001</v>
       </c>
     </row>
     <row r="19">
@@ -749,10 +749,10 @@
         <v>46445.16666666666</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2.781039953231812</v>
+        <v>3.539</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>96.3450565651795</v>
+        <v>97.535</v>
       </c>
     </row>
     <row r="20">
@@ -763,10 +763,10 @@
         <v>46445.20833333334</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.746127843856812</v>
+        <v>3.07</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>96.34787739159304</v>
+        <v>97.449</v>
       </c>
     </row>
     <row r="21">
@@ -777,10 +777,10 @@
         <v>46445.25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2.692874670028687</v>
+        <v>3.312</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>96.38237826849718</v>
+        <v>97.518</v>
       </c>
     </row>
     <row r="22">
@@ -791,10 +791,10 @@
         <v>46445.29166666666</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2.646213293075562</v>
+        <v>3.558</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>96.39856678744859</v>
+        <v>97.56699999999999</v>
       </c>
     </row>
     <row r="23">
@@ -805,10 +805,10 @@
         <v>46445.33333333334</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2.614566564559937</v>
+        <v>3.176</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>96.39224787326812</v>
+        <v>97.627</v>
       </c>
     </row>
     <row r="24">
@@ -819,10 +819,10 @@
         <v>46445.375</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2.609561681747437</v>
+        <v>3.076</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>96.382641282615</v>
+        <v>97.556</v>
       </c>
     </row>
     <row r="25">
@@ -833,10 +833,10 @@
         <v>46445.41666666666</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2.642886877059937</v>
+        <v>3.145</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>96.32377872304842</v>
+        <v>97.438</v>
       </c>
     </row>
     <row r="26">
@@ -847,10 +847,10 @@
         <v>46445.45833333334</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2.701205968856812</v>
+        <v>3.149</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>96.34084176394155</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="27">
@@ -861,10 +861,10 @@
         <v>46445.5</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2.792667150497437</v>
+        <v>3.457</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>96.34100614776519</v>
+        <v>97.54600000000001</v>
       </c>
     </row>
     <row r="28">
@@ -875,10 +875,10 @@
         <v>46445.54166666666</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2.895663976669312</v>
+        <v>3.219</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>96.30910253527445</v>
+        <v>97.413</v>
       </c>
     </row>
     <row r="29">
@@ -889,10 +889,10 @@
         <v>46445.58333333334</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3.049869298934937</v>
+        <v>3.714</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>96.31252171880602</v>
+        <v>97.425</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         <v>46445.625</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3.109500646591187</v>
+        <v>3.554</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>96.29232223455797</v>
+        <v>97.515</v>
       </c>
     </row>
     <row r="31">
@@ -917,10 +917,10 @@
         <v>46445.66666666666</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3.160770177841187</v>
+        <v>3.723</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>96.25302135000375</v>
+        <v>97.303</v>
       </c>
     </row>
     <row r="32">
@@ -931,10 +931,10 @@
         <v>46445.70833333334</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3.182285070419312</v>
+        <v>4.007</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>96.1748404034838</v>
+        <v>97.27500000000001</v>
       </c>
     </row>
     <row r="33">
@@ -945,10 +945,10 @@
         <v>46445.75</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3.152499914169312</v>
+        <v>3.685</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>96.19194947184755</v>
+        <v>97.21599999999999</v>
       </c>
     </row>
     <row r="34">
@@ -959,10 +959,10 @@
         <v>46445.79166666666</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3.099551916122437</v>
+        <v>3.683</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>96.2124974498017</v>
+        <v>97.459</v>
       </c>
     </row>
     <row r="35">
@@ -973,10 +973,10 @@
         <v>46445.83333333334</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3.030032873153687</v>
+        <v>3.495</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>96.22752213128177</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -987,10 +987,10 @@
         <v>46445.875</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2.963687658309937</v>
+        <v>3.546</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>96.22871227016488</v>
+        <v>97.262</v>
       </c>
     </row>
     <row r="37">
@@ -1001,10 +1001,10 @@
         <v>46445.91666666666</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2.907291173934937</v>
+        <v>3.33</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>96.23975228776008</v>
+        <v>97.55200000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1015,10 +1015,10 @@
         <v>46445.95833333334</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2.849185705184937</v>
+        <v>3.461</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>96.24602517446992</v>
+        <v>97.42400000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1029,10 +1029,10 @@
         <v>46446</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>2.749454259872437</v>
+        <v>3.37</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>96.22212376651366</v>
+        <v>97.477</v>
       </c>
     </row>
     <row r="40">
@@ -1043,10 +1043,10 @@
         <v>46446.04166666666</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>2.641238927841187</v>
+        <v>3.354</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>96.24906956288361</v>
+        <v>97.32899999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1057,10 +1057,10 @@
         <v>46446.08333333334</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>2.557864904403687</v>
+        <v>3.206</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>96.23534022593377</v>
+        <v>97.33799999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1071,10 +1071,10 @@
         <v>46446.125</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>2.481113195419312</v>
+        <v>3.225</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>96.22194623198413</v>
+        <v>97.327</v>
       </c>
     </row>
     <row r="43">
@@ -1085,10 +1085,10 @@
         <v>46446.16666666666</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>2.397525548934937</v>
+        <v>2.849</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>96.1429104895813</v>
+        <v>97.175</v>
       </c>
     </row>
     <row r="44">
@@ -1099,10 +1099,10 @@
         <v>46446.20833333334</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2.298831701278687</v>
+        <v>2.861</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>96.09103753019561</v>
+        <v>97.099</v>
       </c>
     </row>
     <row r="45">
@@ -1113,10 +1113,10 @@
         <v>46446.25</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>2.203281164169312</v>
+        <v>2.951</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>96.11392633379829</v>
+        <v>97.26600000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1127,10 +1127,10 @@
         <v>46446.29166666666</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>2.110996007919312</v>
+        <v>2.79</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>96.11368304573931</v>
+        <v>97.337</v>
       </c>
     </row>
     <row r="47">
@@ -1141,10 +1141,10 @@
         <v>46446.33333333334</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>2.030338048934937</v>
+        <v>2.751</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>96.12336854062778</v>
+        <v>97.288</v>
       </c>
     </row>
     <row r="48">
@@ -1155,10 +1155,10 @@
         <v>46446.375</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1.993350863456726</v>
+        <v>2.434</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>96.17733903760303</v>
+        <v>97.348</v>
       </c>
     </row>
     <row r="49">
@@ -1169,10 +1169,10 @@
         <v>46446.41666666666</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>2.043796300888062</v>
+        <v>2.717</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>96.14273295505177</v>
+        <v>97.369</v>
       </c>
     </row>
     <row r="50">
@@ -1183,10 +1183,10 @@
         <v>46446.45833333334</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>2.161350011825562</v>
+        <v>2.424</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>96.12568964021747</v>
+        <v>97.26900000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1197,10 +1197,10 @@
         <v>46446.5</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>2.293796300888062</v>
+        <v>2.706</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>96.08143093954247</v>
+        <v>97.34099999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1211,10 +1211,10 @@
         <v>46446.54166666666</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>2.430972814559937</v>
+        <v>3.118</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>95.97679734812348</v>
+        <v>97.086</v>
       </c>
     </row>
     <row r="53">
@@ -1225,10 +1225,10 @@
         <v>46446.58333333334</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>2.607913732528687</v>
+        <v>3.459</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>95.93018467109405</v>
+        <v>97.276</v>
       </c>
     </row>
     <row r="54">
@@ -1239,10 +1239,10 @@
         <v>46446.625</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>2.731143712997437</v>
+        <v>3.193</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>95.87603663958927</v>
+        <v>97.066</v>
       </c>
     </row>
     <row r="55">
@@ -1253,10 +1253,10 @@
         <v>46446.66666666666</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>2.812625646591187</v>
+        <v>3.241</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>95.84300206639195</v>
+        <v>97.005</v>
       </c>
     </row>
     <row r="56">
@@ -1267,10 +1267,10 @@
         <v>46446.70833333334</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>2.864139318466187</v>
+        <v>3.276</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>95.85036646169071</v>
+        <v>97.062</v>
       </c>
     </row>
     <row r="57">
@@ -1281,10 +1281,10 @@
         <v>46446.75</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>2.879092931747437</v>
+        <v>3.61</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>95.88379555606477</v>
+        <v>97.13500000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1295,10 +1295,10 @@
         <v>46446.79166666666</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>2.837558507919312</v>
+        <v>3.382</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>95.92825809268106</v>
+        <v>97.078</v>
       </c>
     </row>
     <row r="59">
@@ -1309,10 +1309,10 @@
         <v>46446.83333333334</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>2.754459142684937</v>
+        <v>3.454</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>95.95188333581363</v>
+        <v>97.08499999999999</v>
       </c>
     </row>
     <row r="60">
@@ -1323,10 +1323,10 @@
         <v>46446.875</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>2.647891759872437</v>
+        <v>3.513</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>95.97425926188659</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="61">
@@ -1337,10 +1337,10 @@
         <v>46446.91666666666</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>2.549533605575562</v>
+        <v>3.295</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>95.98306365948038</v>
+        <v>97.21299999999999</v>
       </c>
     </row>
     <row r="62">
@@ -1351,10 +1351,10 @@
         <v>46446.95833333334</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2.449344396591187</v>
+        <v>3.091</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>95.9731019997682</v>
+        <v>96.979</v>
       </c>
     </row>
     <row r="63">
@@ -1365,10 +1365,10 @@
         <v>46447</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>2.352390050888062</v>
+        <v>2.715</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>96.02393605338854</v>
+        <v>97.274</v>
       </c>
     </row>
     <row r="64">
@@ -1379,10 +1379,10 @@
         <v>46447.04166666666</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2.258609533309937</v>
+        <v>3.081</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>96.01428343526479</v>
+        <v>97.182</v>
       </c>
     </row>
     <row r="65">
@@ -1393,10 +1393,10 @@
         <v>46447.08333333334</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>2.159671545028687</v>
+        <v>2.76</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>95.98104502612615</v>
+        <v>97.059</v>
       </c>
     </row>
     <row r="66">
@@ -1407,10 +1407,10 @@
         <v>46447.125</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>2.058933019638062</v>
+        <v>2.466</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>95.95703841252276</v>
+        <v>97.13500000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1421,10 +1421,10 @@
         <v>46447.16666666666</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1.957980990409851</v>
+        <v>2.652</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>95.94699127322231</v>
+        <v>97.10299999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1435,10 +1435,10 @@
         <v>46447.20833333334</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>1.856937289237976</v>
+        <v>2.419</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>95.98355023559833</v>
+        <v>97.122</v>
       </c>
     </row>
     <row r="69">
@@ -1449,10 +1449,10 @@
         <v>46447.25</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>1.754001498222351</v>
+        <v>2.399</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>95.99202586554486</v>
+        <v>97.20099999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1463,10 +1463,10 @@
         <v>46447.29166666666</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>1.654331088066101</v>
+        <v>2.242</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>95.99132887813265</v>
+        <v>97.209</v>
       </c>
     </row>
     <row r="71">
@@ -1477,10 +1477,10 @@
         <v>46447.33333333334</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1.568027377128601</v>
+        <v>2.271</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>96.0053343799062</v>
+        <v>97.089</v>
       </c>
     </row>
     <row r="72">
@@ -1491,10 +1491,10 @@
         <v>46447.375</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>1.529056429862976</v>
+        <v>2.202</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>95.97525871553427</v>
+        <v>97.074</v>
       </c>
     </row>
     <row r="73">
@@ -1505,10 +1505,10 @@
         <v>46447.41666666666</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>1.542606234550476</v>
+        <v>2.321</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>95.97132007912002</v>
+        <v>96.968</v>
       </c>
     </row>
     <row r="74">
@@ -1519,10 +1519,10 @@
         <v>46447.45833333334</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>1.620487093925476</v>
+        <v>2.272</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>95.93821975239324</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="75">
@@ -1533,10 +1533,10 @@
         <v>46447.5</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>1.752323031425476</v>
+        <v>2.497</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>95.91732985608593</v>
+        <v>97.13500000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1547,10 +1547,10 @@
         <v>46447.54166666666</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1.909152865409851</v>
+        <v>2.253</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>95.86979005429122</v>
+        <v>96.884</v>
       </c>
     </row>
     <row r="77">
@@ -1561,10 +1561,10 @@
         <v>46447.58333333334</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2.124423742294312</v>
+        <v>2.542</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>95.78800581435723</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="78">
@@ -1575,10 +1575,10 @@
         <v>46447.625</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2.278720617294312</v>
+        <v>2.789</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>95.76356522745944</v>
+        <v>96.95099999999999</v>
       </c>
     </row>
     <row r="79">
@@ -1589,10 +1589,10 @@
         <v>46447.66666666666</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2.405917882919312</v>
+        <v>3.075</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>95.7609613876931</v>
+        <v>96.904</v>
       </c>
     </row>
     <row r="80">
@@ -1603,10 +1603,10 @@
         <v>46447.70833333334</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>2.487766027450562</v>
+        <v>2.764</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>95.79327267206644</v>
+        <v>96.916</v>
       </c>
     </row>
     <row r="81">
@@ -1617,10 +1617,10 @@
         <v>46447.75</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>2.547855138778687</v>
+        <v>2.946</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>95.81042776790079</v>
+        <v>96.77800000000001</v>
       </c>
     </row>
     <row r="82">
@@ -1631,10 +1631,10 @@
         <v>46447.79166666666</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>2.524509191513062</v>
+        <v>3.201</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>95.86981635570299</v>
+        <v>97.07299999999999</v>
       </c>
     </row>
     <row r="83">
@@ -1645,10 +1645,10 @@
         <v>46447.83333333334</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>2.484439611434937</v>
+        <v>3.014</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>95.89101529359873</v>
+        <v>96.944</v>
       </c>
     </row>
     <row r="84">
@@ -1659,10 +1659,10 @@
         <v>46447.875</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>2.407565832138062</v>
+        <v>3.048</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>95.8916202260697</v>
+        <v>96.98099999999999</v>
       </c>
     </row>
     <row r="85">
@@ -1673,10 +1673,10 @@
         <v>46447.91666666666</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2.335635900497437</v>
+        <v>2.874</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>95.88314459612317</v>
+        <v>96.92</v>
       </c>
     </row>
     <row r="86">
@@ -1687,10 +1687,10 @@
         <v>46447.95833333334</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2.261966466903687</v>
+        <v>2.782</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>95.88390076171189</v>
+        <v>97.066</v>
       </c>
     </row>
     <row r="87">
@@ -1701,10 +1701,10 @@
         <v>46448</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>2.183170080184937</v>
+        <v>2.75</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>95.86107771163866</v>
+        <v>97.06699999999999</v>
       </c>
     </row>
     <row r="88">
@@ -1715,10 +1715,10 @@
         <v>46448.04166666666</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2.102603673934937</v>
+        <v>2.552</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>95.8381363052124</v>
+        <v>97.038</v>
       </c>
     </row>
     <row r="89">
@@ -1729,10 +1729,10 @@
         <v>46448.08333333334</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2.016879796981812</v>
+        <v>2.597</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>95.84755878598305</v>
+        <v>96.973</v>
       </c>
     </row>
     <row r="90">
@@ -1743,10 +1743,10 @@
         <v>46448.125</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1.925998568534851</v>
+        <v>2.259</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>95.80074884836527</v>
+        <v>97.027</v>
       </c>
     </row>
     <row r="91">
@@ -1757,10 +1757,10 @@
         <v>46448.16666666666</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>1.834995150566101</v>
+        <v>2.285</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>95.78189731147101</v>
+        <v>97.006</v>
       </c>
     </row>
     <row r="92">
@@ -1771,10 +1771,10 @@
         <v>46448.20833333334</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1.738803744316101</v>
+        <v>2.203</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>95.80005843630602</v>
+        <v>96.937</v>
       </c>
     </row>
     <row r="93">
@@ -1785,10 +1785,10 @@
         <v>46448.25</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>1.644168734550476</v>
+        <v>2.282</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>95.8229472399087</v>
+        <v>96.994</v>
       </c>
     </row>
     <row r="94">
@@ -1799,10 +1799,10 @@
         <v>46448.29166666666</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>1.549381136894226</v>
+        <v>2.134</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>95.85981524387316</v>
+        <v>97.02500000000001</v>
       </c>
     </row>
     <row r="95">
@@ -1813,10 +1813,10 @@
         <v>46448.33333333334</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1.471408724784851</v>
+        <v>2.238</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>95.89290899524698</v>
+        <v>97.235</v>
       </c>
     </row>
     <row r="96">
@@ -1827,10 +1827,10 @@
         <v>46448.375</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>1.440860629081726</v>
+        <v>1.978</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>95.90058243213419</v>
+        <v>96.988</v>
       </c>
     </row>
     <row r="97">
@@ -1841,10 +1841,10 @@
         <v>46448.41666666666</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.462955355644226</v>
+        <v>2.206</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>95.86914566970258</v>
+        <v>97.06399999999999</v>
       </c>
     </row>
     <row r="98">
@@ -1855,10 +1855,10 @@
         <v>46448.45833333334</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.547672152519226</v>
+        <v>2.16</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>95.83641356274073</v>
+        <v>97.036</v>
       </c>
     </row>
     <row r="99">
@@ -1869,10 +1869,10 @@
         <v>46448.5</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>1.686435580253601</v>
+        <v>2.517</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>95.82056038678955</v>
+        <v>96.926</v>
       </c>
     </row>
     <row r="100">
@@ -1883,10 +1883,10 @@
         <v>46448.54166666666</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>1.848514437675476</v>
+        <v>2.465</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>95.76397289934205</v>
+        <v>96.93600000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1897,10 +1897,10 @@
         <v>46448.58333333334</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>2.085819005966187</v>
+        <v>2.569</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>95.74865890233238</v>
+        <v>97.01600000000001</v>
       </c>
     </row>
     <row r="102">
@@ -1911,10 +1911,10 @@
         <v>46448.625</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>2.267001867294312</v>
+        <v>2.797</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>95.73029394155608</v>
+        <v>96.953</v>
       </c>
     </row>
     <row r="103">
@@ -1925,10 +1925,10 @@
         <v>46448.66666666666</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>2.397525548934937</v>
+        <v>2.981</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>95.73721121285458</v>
+        <v>96.71299999999999</v>
       </c>
     </row>
     <row r="104">
@@ -1939,10 +1939,10 @@
         <v>46448.70833333334</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>2.487766027450562</v>
+        <v>2.977</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>95.76062604469288</v>
+        <v>96.97799999999999</v>
       </c>
     </row>
     <row r="105">
@@ -1953,10 +1953,10 @@
         <v>46448.75</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>2.554538488388062</v>
+        <v>3.138</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>95.81078283695985</v>
+        <v>96.886</v>
       </c>
     </row>
     <row r="106">
@@ -1967,10 +1967,10 @@
         <v>46448.79166666666</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>2.552860021591187</v>
+        <v>3.338</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>95.87597088605982</v>
+        <v>96.991</v>
       </c>
     </row>
     <row r="107">
@@ -1981,10 +1981,10 @@
         <v>46448.83333333334</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>2.531162023544312</v>
+        <v>3.175</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>95.88882570106794</v>
+        <v>96.926</v>
       </c>
     </row>
     <row r="108">
@@ -1995,10 +1995,10 @@
         <v>46448.875</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2.477756261825562</v>
+        <v>2.921</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>95.92797535250442</v>
+        <v>97.062</v>
       </c>
     </row>
     <row r="109">
@@ -2009,10 +2009,10 @@
         <v>46448.91666666666</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>2.420963048934937</v>
+        <v>2.85</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>95.92963891679959</v>
+        <v>97.09399999999999</v>
       </c>
     </row>
     <row r="110">
@@ -2023,10 +2023,10 @@
         <v>46448.95833333334</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2.357394933700562</v>
+        <v>3.063</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>95.94025811180629</v>
+        <v>97.14400000000001</v>
       </c>
     </row>
     <row r="111">
@@ -2037,10 +2037,10 @@
         <v>46449</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2.295474767684937</v>
+        <v>2.752</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>95.96494856211599</v>
+        <v>97.09099999999999</v>
       </c>
     </row>
     <row r="112">
@@ -2051,10 +2051,10 @@
         <v>46449.04166666666</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2.228427648544312</v>
+        <v>2.702</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>95.93808166998139</v>
+        <v>97.155</v>
       </c>
     </row>
     <row r="113">
@@ -2065,10 +2065,10 @@
         <v>46449.08333333334</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>2.166385412216187</v>
+        <v>2.99</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>95.99073052101463</v>
+        <v>97.214</v>
       </c>
     </row>
     <row r="114">
@@ -2079,10 +2079,10 @@
         <v>46449.125</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.105960607528687</v>
+        <v>2.793</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>95.90359394378315</v>
+        <v>97.011</v>
       </c>
     </row>
     <row r="115">
@@ -2093,10 +2093,10 @@
         <v>46449.16666666666</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>2.052219152450562</v>
+        <v>2.611</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>95.86808703787837</v>
+        <v>96.98399999999999</v>
       </c>
     </row>
     <row r="116">
@@ -2107,10 +2107,10 @@
         <v>46449.20833333334</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>2.006808996200562</v>
+        <v>2.353</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>95.87499773382392</v>
+        <v>97.06100000000001</v>
       </c>
     </row>
     <row r="117">
@@ -2121,10 +2121,10 @@
         <v>46449.25</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1.957980990409851</v>
+        <v>2.906</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>95.84441576727519</v>
+        <v>96.83499999999999</v>
       </c>
     </row>
     <row r="118">
@@ -2135,10 +2135,10 @@
         <v>46449.29166666666</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>1.924320101737976</v>
+        <v>2.528</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>95.81464256913875</v>
+        <v>97.04300000000001</v>
       </c>
     </row>
     <row r="119">
@@ -2149,10 +2149,10 @@
         <v>46449.33333333334</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>1.936099886894226</v>
+        <v>2.537</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>95.85257578028035</v>
+        <v>97</v>
       </c>
     </row>
     <row r="120">
@@ -2163,10 +2163,10 @@
         <v>46449.375</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>1.995029330253601</v>
+        <v>2.643</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>95.83706452268231</v>
+        <v>96.90900000000001</v>
       </c>
     </row>
     <row r="121">
@@ -2177,10 +2177,10 @@
         <v>46449.41666666666</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>2.087466955184937</v>
+        <v>2.666</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>95.80003213489424</v>
+        <v>96.873</v>
       </c>
     </row>
     <row r="122">
@@ -2191,10 +2191,10 @@
         <v>46449.45833333334</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>2.204990148544312</v>
+        <v>3.007</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>95.77363209281874</v>
+        <v>96.952</v>
       </c>
     </row>
     <row r="123">
@@ -2205,10 +2205,10 @@
         <v>46449.5</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2.357394933700562</v>
+        <v>2.741</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>95.7117711723091</v>
+        <v>96.977</v>
       </c>
     </row>
     <row r="124">
@@ -2219,10 +2219,10 @@
         <v>46449.54166666666</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2.542850255966187</v>
+        <v>2.889</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>95.63762749249759</v>
+        <v>96.848</v>
       </c>
     </row>
     <row r="125">
@@ -2233,10 +2233,10 @@
         <v>46449.58333333334</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2.777713537216187</v>
+        <v>3.321</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>95.59866195094357</v>
+        <v>96.81100000000001</v>
       </c>
     </row>
     <row r="126">
@@ -2247,10 +2247,10 @@
         <v>46449.625</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>2.976962804794312</v>
+        <v>3.29</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>95.58576768381778</v>
+        <v>96.797</v>
       </c>
     </row>
     <row r="127">
@@ -2261,10 +2261,10 @@
         <v>46449.66666666666</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>3.127689123153687</v>
+        <v>3.62</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>95.6122729315404</v>
+        <v>96.76000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -2275,10 +2275,10 @@
         <v>46449.70833333334</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>3.223605871200562</v>
+        <v>3.746</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>95.6219189743112</v>
+        <v>96.818</v>
       </c>
     </row>
     <row r="129">
@@ -2289,10 +2289,10 @@
         <v>46449.75</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>3.271487951278687</v>
+        <v>3.627</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>95.6290729583157</v>
+        <v>96.708</v>
       </c>
     </row>
     <row r="130">
@@ -2303,10 +2303,10 @@
         <v>46449.79166666666</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>3.291293859481812</v>
+        <v>3.522</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>95.63942256385165</v>
+        <v>96.703</v>
       </c>
     </row>
     <row r="131">
@@ -2317,10 +2317,10 @@
         <v>46449.83333333334</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>3.299564123153687</v>
+        <v>3.848</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>95.58388713287542</v>
+        <v>96.815</v>
       </c>
     </row>
     <row r="132">
@@ -2331,10 +2331,10 @@
         <v>46449.875</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>3.274783849716187</v>
+        <v>3.822</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>95.5779364384599</v>
+        <v>96.72199999999999</v>
       </c>
     </row>
     <row r="133">
@@ -2345,10 +2345,10 @@
         <v>46449.91666666666</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>3.228549718856812</v>
+        <v>3.742</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>95.58019835987309</v>
+        <v>96.84699999999999</v>
       </c>
     </row>
     <row r="134">
@@ -2359,10 +2359,10 @@
         <v>46449.95833333334</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>3.177310705184937</v>
+        <v>3.763</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>95.54489528990962</v>
+        <v>96.71899999999999</v>
       </c>
     </row>
     <row r="135">
@@ -2373,10 +2373,10 @@
         <v>46450</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>3.129337072372437</v>
+        <v>3.848</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>95.48643382687271</v>
+        <v>96.492</v>
       </c>
     </row>
     <row r="136">
@@ -2387,10 +2387,10 @@
         <v>46450.04166666666</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>3.083011388778687</v>
+        <v>3.582</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>95.45604254555941</v>
+        <v>96.604</v>
       </c>
     </row>
     <row r="137">
@@ -2401,10 +2401,10 @@
         <v>46450.08333333334</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>3.041599035263062</v>
+        <v>3.566</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>95.36527637350211</v>
+        <v>96.43899999999999</v>
       </c>
     </row>
     <row r="138">
@@ -2415,10 +2415,10 @@
         <v>46450.125</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2.996860265731812</v>
+        <v>3.407</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>95.27900774285941</v>
+        <v>96.486</v>
       </c>
     </row>
     <row r="139">
@@ -2429,10 +2429,10 @@
         <v>46450.16666666666</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2.958713293075562</v>
+        <v>3.554</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>95.23037643247577</v>
+        <v>96.42100000000001</v>
       </c>
     </row>
     <row r="140">
@@ -2443,10 +2443,10 @@
         <v>46450.20833333334</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>2.930545568466187</v>
+        <v>3.569</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>95.17296045055716</v>
+        <v>96.17700000000001</v>
       </c>
     </row>
     <row r="141">
@@ -2457,10 +2457,10 @@
         <v>46450.25</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>2.905643224716187</v>
+        <v>3.333</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>95.11104035187101</v>
+        <v>96.401</v>
       </c>
     </row>
     <row r="142">
@@ -2471,10 +2471,10 @@
         <v>46450.29166666666</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2.877414464950562</v>
+        <v>3.503</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>95.12355982387891</v>
+        <v>96.327</v>
       </c>
     </row>
     <row r="143">
@@ -2485,10 +2485,10 @@
         <v>46450.33333333334</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>2.875766515731812</v>
+        <v>3.08</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>95.14212204524357</v>
+        <v>96.372</v>
       </c>
     </row>
     <row r="144">
@@ -2499,10 +2499,10 @@
         <v>46450.375</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>2.908969640731812</v>
+        <v>3.476</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>95.15318178889761</v>
+        <v>96.316</v>
       </c>
     </row>
     <row r="145">
@@ -2513,10 +2513,10 @@
         <v>46450.41666666666</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>2.993564367294312</v>
+        <v>3.473</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>95.14826342489451</v>
+        <v>96.40900000000001</v>
       </c>
     </row>
     <row r="146">
@@ -2527,10 +2527,10 @@
         <v>46450.45833333334</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>3.102878332138062</v>
+        <v>3.651</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>95.14927602924809</v>
+        <v>96.227</v>
       </c>
     </row>
     <row r="147">
@@ -2541,10 +2541,10 @@
         <v>46450.5</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>3.230197668075562</v>
+        <v>3.498</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>95.20250351134052</v>
+        <v>96.245</v>
       </c>
     </row>
     <row r="148">
@@ -2555,10 +2555,10 @@
         <v>46450.54166666666</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>3.354007482528687</v>
+        <v>3.664</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>95.19490897868866</v>
+        <v>96.46599999999999</v>
       </c>
     </row>
     <row r="149">
@@ -2569,10 +2569,10 @@
         <v>46450.58333333334</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>3.502292394638062</v>
+        <v>3.813</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>95.26784936891119</v>
+        <v>96.247</v>
       </c>
     </row>
     <row r="150">
@@ -2583,10 +2583,10 @@
         <v>46450.625</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>3.609195470809937</v>
+        <v>4.411</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>95.3106746426441</v>
+        <v>96.47199999999999</v>
       </c>
     </row>
     <row r="151">
@@ -2597,10 +2597,10 @@
         <v>46450.66666666666</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>3.663394689559937</v>
+        <v>4.328</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>95.39742327405182</v>
+        <v>96.473</v>
       </c>
     </row>
     <row r="152">
@@ -2611,10 +2611,10 @@
         <v>46450.70833333334</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>3.665042638778687</v>
+        <v>4.274</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>95.42082495518423</v>
+        <v>96.491</v>
       </c>
     </row>
     <row r="153">
@@ -2625,10 +2625,10 @@
         <v>46450.75</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>3.653537511825562</v>
+        <v>4.209</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>95.5135308563604</v>
+        <v>96.729</v>
       </c>
     </row>
     <row r="154">
@@ -2639,10 +2639,10 @@
         <v>46450.79166666666</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>3.609195470809937</v>
+        <v>4.245</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>95.60454689182964</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -2653,10 +2653,10 @@
         <v>46450.83333333334</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>3.536838293075562</v>
+        <v>4.119</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>95.66611849680969</v>
+        <v>96.81100000000001</v>
       </c>
     </row>
     <row r="156">
@@ -2667,10 +2667,10 @@
         <v>46450.875</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>3.461124181747437</v>
+        <v>3.751</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>95.71352021619255</v>
+        <v>96.962</v>
       </c>
     </row>
     <row r="157">
@@ -2681,10 +2681,10 @@
         <v>46450.91666666666</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>3.382022619247437</v>
+        <v>3.841</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>95.77939867735179</v>
+        <v>96.93600000000001</v>
       </c>
     </row>
     <row r="158">
@@ -2695,10 +2695,10 @@
         <v>46450.95833333334</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>3.322665929794312</v>
+        <v>3.596</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>95.83229081644402</v>
+        <v>97.057</v>
       </c>
     </row>
     <row r="159">
@@ -2709,10 +2709,10 @@
         <v>46451</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>3.289645910263062</v>
+        <v>3.923</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>95.85391057692824</v>
+        <v>97.01000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -2723,10 +2723,10 @@
         <v>46451.04166666666</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>3.253329992294312</v>
+        <v>3.788</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>95.91266135549475</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -2737,10 +2737,10 @@
         <v>46451.08333333334</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>3.212009191513062</v>
+        <v>3.624</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>95.9524882682846</v>
+        <v>97.15300000000001</v>
       </c>
     </row>
     <row r="162">
@@ -2751,10 +2751,10 @@
         <v>46451.125</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>3.182285070419312</v>
+        <v>3.63</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>95.97426583723953</v>
+        <v>97.095</v>
       </c>
     </row>
     <row r="163">
@@ -2765,10 +2765,10 @@
         <v>46451.16666666666</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>3.157474279403687</v>
+        <v>3.586</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>96.0056236954358</v>
+        <v>97.215</v>
       </c>
     </row>
     <row r="164">
@@ -2779,10 +2779,10 @@
         <v>46451.20833333334</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>3.147525548934937</v>
+        <v>3.618</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>96.03309552004137</v>
+        <v>97.23399999999999</v>
       </c>
     </row>
     <row r="165">
@@ -2793,10 +2793,10 @@
         <v>46451.25</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>3.129337072372437</v>
+        <v>3.789</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>96.11144085038495</v>
+        <v>97.20999999999999</v>
       </c>
     </row>
     <row r="166">
@@ -2807,10 +2807,10 @@
         <v>46451.29166666666</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>3.106174230575562</v>
+        <v>3.77</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>96.16153846447541</v>
+        <v>97.316</v>
       </c>
     </row>
     <row r="167">
@@ -2821,10 +2821,10 @@
         <v>46451.33333333334</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>3.106174230575562</v>
+        <v>3.63</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>96.24550572158724</v>
+        <v>97.369</v>
       </c>
     </row>
     <row r="168">
@@ -2835,10 +2835,10 @@
         <v>46451.375</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>3.111148595809937</v>
+        <v>3.6</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>96.32039241628158</v>
+        <v>97.363</v>
       </c>
     </row>
     <row r="169">
@@ -2849,10 +2849,10 @@
         <v>46451.41666666666</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>3.169040441513062</v>
+        <v>3.462</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>96.38873005944237</v>
+        <v>97.596</v>
       </c>
     </row>
     <row r="170">
@@ -2863,10 +2863,10 @@
         <v>46451.45833333334</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>3.235141515731812</v>
+        <v>3.688</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>96.42017997257987</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="171">
@@ -2877,10 +2877,10 @@
         <v>46451.5</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>3.357303380966187</v>
+        <v>3.995</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>96.47786554396923</v>
+        <v>97.70399999999999</v>
       </c>
     </row>
     <row r="172">
@@ -2891,10 +2891,10 @@
         <v>46451.54166666666</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>3.459476232528687</v>
+        <v>3.932</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>96.45051207571667</v>
+        <v>97.611</v>
       </c>
     </row>
     <row r="173">
@@ -2905,10 +2905,10 @@
         <v>46451.58333333334</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>3.630557775497437</v>
+        <v>3.878</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>96.48739323038701</v>
+        <v>97.56399999999999</v>
       </c>
     </row>
     <row r="174">
@@ -2919,10 +2919,10 @@
         <v>46451.625</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>3.681461095809937</v>
+        <v>4.326</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>96.55067442713285</v>
+        <v>97.752</v>
       </c>
     </row>
     <row r="175">
@@ -2933,10 +2933,10 @@
         <v>46451.66666666666</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>3.748752355575562</v>
+        <v>4.188</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>96.61947892035276</v>
+        <v>97.806</v>
       </c>
     </row>
     <row r="176">
@@ -2947,10 +2947,10 @@
         <v>46451.70833333334</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>3.755313634872437</v>
+        <v>4.232</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>96.59183613657061</v>
+        <v>97.63500000000001</v>
       </c>
     </row>
     <row r="177">
@@ -2961,10 +2961,10 @@
         <v>46451.75</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>3.696231603622437</v>
+        <v>4.36</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>96.68209600645112</v>
+        <v>97.97199999999999</v>
       </c>
     </row>
     <row r="178">
@@ -2975,10 +2975,10 @@
         <v>46451.79166666666</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>3.610812902450562</v>
+        <v>4.064</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>96.71966099782777</v>
+        <v>97.824</v>
       </c>
     </row>
     <row r="179">
@@ -2989,10 +2989,10 @@
         <v>46451.83333333334</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>3.489108800888062</v>
+        <v>4.108</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>96.75066378696499</v>
+        <v>97.884</v>
       </c>
     </row>
     <row r="180">
@@ -3003,10 +3003,10 @@
         <v>46451.875</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>3.398532629013062</v>
+        <v>3.836</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>96.75994160997085</v>
+        <v>97.999</v>
       </c>
     </row>
     <row r="181">
@@ -3017,10 +3017,10 @@
         <v>46451.91666666666</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>3.354007482528687</v>
+        <v>3.645</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>96.76694436085762</v>
+        <v>97.863</v>
       </c>
     </row>
     <row r="182">
@@ -3031,10 +3031,10 @@
         <v>46451.95833333334</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>3.335849523544312</v>
+        <v>3.853</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>96.75199200825995</v>
+        <v>97.809</v>
       </c>
     </row>
     <row r="183">
@@ -3045,10 +3045,10 @@
         <v>46452</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>3.319339513778687</v>
+        <v>3.721</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>96.7511306370241</v>
+        <v>97.73999999999999</v>
       </c>
     </row>
     <row r="184">
@@ -3059,10 +3059,10 @@
         <v>46452.04166666666</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>3.307803869247437</v>
+        <v>4.057</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>96.77853013274729</v>
+        <v>97.92400000000001</v>
       </c>
     </row>
     <row r="185">
@@ -3073,10 +3073,10 @@
         <v>46452.08333333334</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>3.296237707138062</v>
+        <v>3.623</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>96.80126112787929</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="186">
@@ -3087,10 +3087,10 @@
         <v>46452.125</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>3.278079748153687</v>
+        <v>3.907</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>96.78164685004337</v>
+        <v>97.968</v>
       </c>
     </row>
     <row r="187">
@@ -3101,10 +3101,10 @@
         <v>46452.16666666666</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>3.259952306747437</v>
+        <v>3.857</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>96.77136957338983</v>
+        <v>97.919</v>
       </c>
     </row>
     <row r="188">
@@ -3115,10 +3115,10 @@
         <v>46452.20833333334</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>3.210361242294312</v>
+        <v>3.583</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>96.79677016181763</v>
+        <v>97.985</v>
       </c>
     </row>
     <row r="189">
@@ -3129,10 +3129,10 @@
         <v>46452.25</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>3.180606603622437</v>
+        <v>3.688</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>96.79053672722546</v>
+        <v>97.907</v>
       </c>
     </row>
     <row r="190">
@@ -3143,10 +3143,10 @@
         <v>46452.29166666666</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>3.145877599716187</v>
+        <v>3.974</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>96.77938492863018</v>
+        <v>97.88800000000001</v>
       </c>
     </row>
     <row r="191">
@@ -3157,10 +3157,10 @@
         <v>46452.33333333334</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>3.142581701278687</v>
+        <v>3.72</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>96.82587267395365</v>
+        <v>97.991</v>
       </c>
     </row>
     <row r="192">
@@ -3171,10 +3171,10 @@
         <v>46452.375</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>3.203769445419312</v>
+        <v>3.649</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>96.81040744382624</v>
+        <v>97.965</v>
       </c>
     </row>
     <row r="193">
@@ -3185,10 +3185,10 @@
         <v>46452.41666666666</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>3.312747716903687</v>
+        <v>3.834</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>96.83945077778576</v>
+        <v>98.092</v>
       </c>
     </row>
     <row r="194">
@@ -3199,10 +3199,10 @@
         <v>46452.45833333334</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>3.467715978622437</v>
+        <v>3.813</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>96.84286338596438</v>
+        <v>98.023</v>
       </c>
     </row>
     <row r="195">
@@ -3213,10 +3213,10 @@
         <v>46452.5</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>3.635471105575562</v>
+        <v>4.365</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>96.86558780574343</v>
+        <v>98.00700000000001</v>
       </c>
     </row>
     <row r="196">
@@ -3227,10 +3227,10 @@
         <v>46452.54166666666</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>3.883121252059937</v>
+        <v>4.275</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>96.82708911424854</v>
+        <v>98.044</v>
       </c>
     </row>
     <row r="197">
@@ -3241,10 +3241,10 @@
         <v>46452.58333333334</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>4.121799468994141</v>
+        <v>4.51</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>96.78338274322094</v>
+        <v>97.898</v>
       </c>
     </row>
     <row r="198">
@@ -3255,10 +3255,10 @@
         <v>46452.625</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>4.221286773681641</v>
+        <v>5.052</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>96.80249071888007</v>
+        <v>98.008</v>
       </c>
     </row>
     <row r="199">
@@ -3269,10 +3269,10 @@
         <v>46452.66666666666</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>4.338565826416016</v>
+        <v>4.873</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>96.81316251671034</v>
+        <v>97.977</v>
       </c>
     </row>
     <row r="200">
@@ -3283,10 +3283,10 @@
         <v>46452.70833333334</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>4.400394439697266</v>
+        <v>5.018</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>96.78832083328288</v>
+        <v>97.896</v>
       </c>
     </row>
     <row r="201">
@@ -3297,10 +3297,10 @@
         <v>46452.75</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>4.408512115478516</v>
+        <v>4.799</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>96.83540693572438</v>
+        <v>97.881</v>
       </c>
     </row>
     <row r="202">
@@ -3311,10 +3311,10 @@
         <v>46452.79166666666</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>4.372745513916016</v>
+        <v>4.838</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>96.83824748819676</v>
+        <v>97.913</v>
       </c>
     </row>
     <row r="203">
@@ -3325,10 +3325,10 @@
         <v>46452.83333333334</v>
       </c>
       <c r="C203" s="2" t="n">
-        <v>4.312534332275391</v>
+        <v>5.028</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>96.81649622065362</v>
+        <v>98.057</v>
       </c>
     </row>
     <row r="204">
@@ -3339,10 +3339,10 @@
         <v>46452.875</v>
       </c>
       <c r="C204" s="2" t="n">
-        <v>4.281589508056641</v>
+        <v>5.015</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>96.80090605882025</v>
+        <v>97.982</v>
       </c>
     </row>
     <row r="205">
@@ -3353,10 +3353,10 @@
         <v>46452.91666666666</v>
       </c>
       <c r="C205" s="2" t="n">
-        <v>4.275058746337891</v>
+        <v>4.841</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>96.75857393655822</v>
+        <v>98.03100000000001</v>
       </c>
     </row>
     <row r="206">
@@ -3367,10 +3367,10 @@
         <v>46452.95833333334</v>
       </c>
       <c r="C206" s="2" t="n">
-        <v>4.229434967041016</v>
+        <v>4.884</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>96.76557011209205</v>
+        <v>97.883</v>
       </c>
     </row>
     <row r="207">
@@ -3381,10 +3381,10 @@
         <v>46453</v>
       </c>
       <c r="C207" s="2" t="n">
-        <v>4.198459625244141</v>
+        <v>4.866</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>96.74997995025868</v>
+        <v>97.881</v>
       </c>
     </row>
     <row r="208">
@@ -3395,10 +3395,10 @@
         <v>46453.04166666666</v>
       </c>
       <c r="C208" s="2" t="n">
-        <v>4.196842193603516</v>
+        <v>4.603</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>96.73123361901155</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="209">
@@ -3409,10 +3409,10 @@
         <v>46453.08333333334</v>
       </c>
       <c r="C209" s="2" t="n">
-        <v>4.224552154541016</v>
+        <v>4.953</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>96.67197653826825</v>
+        <v>97.83199999999999</v>
       </c>
     </row>
     <row r="210">
@@ -3423,10 +3423,10 @@
         <v>46453.125</v>
       </c>
       <c r="C210" s="2" t="n">
-        <v>4.244113922119141</v>
+        <v>4.783</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>96.64030963848356</v>
+        <v>97.797</v>
       </c>
     </row>
     <row r="211">
@@ -3437,10 +3437,10 @@
         <v>46453.16666666666</v>
       </c>
       <c r="C211" s="2" t="n">
-        <v>4.263645172119141</v>
+        <v>4.635</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>96.66932009567834</v>
+        <v>97.759</v>
       </c>
     </row>
     <row r="212">
@@ -3451,10 +3451,10 @@
         <v>46453.20833333334</v>
       </c>
       <c r="C212" s="2" t="n">
-        <v>4.258762359619141</v>
+        <v>4.823</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>96.68772450857232</v>
+        <v>97.786</v>
       </c>
     </row>
     <row r="213">
@@ -3465,10 +3465,10 @@
         <v>46453.25</v>
       </c>
       <c r="C213" s="2" t="n">
-        <v>4.266910552978516</v>
+        <v>4.811</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>96.67413982938727</v>
+        <v>97.904</v>
       </c>
     </row>
     <row r="214">
@@ -3479,10 +3479,10 @@
         <v>46453.29166666666</v>
       </c>
       <c r="C214" s="2" t="n">
-        <v>4.294620513916016</v>
+        <v>4.993</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>96.67089818038522</v>
+        <v>97.749</v>
       </c>
     </row>
     <row r="215">
@@ -3493,10 +3493,10 @@
         <v>46453.33333333334</v>
       </c>
       <c r="C215" s="2" t="n">
-        <v>4.323917388916016</v>
+        <v>4.617</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>96.71440071547151</v>
+        <v>97.937</v>
       </c>
     </row>
     <row r="216">
@@ -3507,10 +3507,10 @@
         <v>46453.375</v>
       </c>
       <c r="C216" s="2" t="n">
-        <v>4.361331939697266</v>
+        <v>4.92</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>96.79098385122575</v>
+        <v>97.958</v>
       </c>
     </row>
     <row r="217">
@@ -3521,10 +3521,10 @@
         <v>46453.41666666666</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>4.468662261962891</v>
+        <v>5.081</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>96.81980362318511</v>
+        <v>97.983</v>
       </c>
     </row>
     <row r="218">
@@ -3535,10 +3535,10 @@
         <v>46453.45833333334</v>
       </c>
       <c r="C218" s="2" t="n">
-        <v>4.609867095947266</v>
+        <v>4.684</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>96.83166555989848</v>
+        <v>98.042</v>
       </c>
     </row>
     <row r="219">
@@ -3549,10 +3549,10 @@
         <v>46453.5</v>
       </c>
       <c r="C219" s="2" t="n">
-        <v>4.770267486572266</v>
+        <v>5.354</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>96.85848642456247</v>
+        <v>98.041</v>
       </c>
     </row>
     <row r="220">
@@ -3563,10 +3563,10 @@
         <v>46453.54166666666</v>
       </c>
       <c r="C220" s="2" t="n">
-        <v>4.909366607666016</v>
+        <v>5.433</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>96.80483811988155</v>
+        <v>97.949</v>
       </c>
     </row>
     <row r="221">
@@ -3577,10 +3577,10 @@
         <v>46453.58333333334</v>
       </c>
       <c r="C221" s="2" t="n">
-        <v>5.086887359619141</v>
+        <v>5.975</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>96.76244024409007</v>
+        <v>97.81100000000001</v>
       </c>
     </row>
     <row r="222">
@@ -3591,10 +3591,10 @@
         <v>46453.625</v>
       </c>
       <c r="C222" s="2" t="n">
-        <v>5.214145660400391</v>
+        <v>5.678</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>96.74082705895879</v>
+        <v>98.074</v>
       </c>
     </row>
     <row r="223">
@@ -3605,10 +3605,10 @@
         <v>46453.66666666666</v>
       </c>
       <c r="C223" s="2" t="n">
-        <v>5.299411773681641</v>
+        <v>5.947</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>96.71707688412026</v>
+        <v>97.842</v>
       </c>
     </row>
     <row r="224">
@@ -3619,10 +3619,10 @@
         <v>46453.70833333334</v>
       </c>
       <c r="C224" s="2" t="n">
-        <v>5.304233551025391</v>
+        <v>5.941</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>96.65196116390268</v>
+        <v>97.545</v>
       </c>
     </row>
     <row r="225">
@@ -3633,10 +3633,10 @@
         <v>46453.75</v>
       </c>
       <c r="C225" s="2" t="n">
-        <v>5.293003082275391</v>
+        <v>5.77</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>96.63739018177583</v>
+        <v>97.79300000000001</v>
       </c>
     </row>
     <row r="226">
@@ -3647,10 +3647,10 @@
         <v>46453.79166666666</v>
       </c>
       <c r="C226" s="2" t="n">
-        <v>5.252780914306641</v>
+        <v>5.643</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>96.58869311786273</v>
+        <v>97.82899999999999</v>
       </c>
     </row>
     <row r="227">
@@ -3661,10 +3661,10 @@
         <v>46453.83333333334</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>5.199649810791016</v>
+        <v>6.037</v>
       </c>
       <c r="D227" s="3" t="n">
-        <v>96.53934509400806</v>
+        <v>97.848</v>
       </c>
     </row>
     <row r="228">
@@ -3675,10 +3675,10 @@
         <v>46453.875</v>
       </c>
       <c r="C228" s="2" t="n">
-        <v>5.138462066650391</v>
+        <v>6.122</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>96.48958939827075</v>
+        <v>97.754</v>
       </c>
     </row>
     <row r="229">
@@ -3689,10 +3689,10 @@
         <v>46453.91666666666</v>
       </c>
       <c r="C229" s="2" t="n">
-        <v>5.064304351806641</v>
+        <v>5.598</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>96.46719374613896</v>
+        <v>97.499</v>
       </c>
     </row>
     <row r="230">
@@ -3703,10 +3703,10 @@
         <v>46453.95833333334</v>
       </c>
       <c r="C230" s="2" t="n">
-        <v>4.998172760009766</v>
+        <v>5.518</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>96.39384568403383</v>
+        <v>97.694</v>
       </c>
     </row>
     <row r="231">
@@ -3717,10 +3717,10 @@
         <v>46454</v>
       </c>
       <c r="C231" s="2" t="n">
-        <v>4.948123931884766</v>
+        <v>5.606</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>96.35866097042339</v>
+        <v>97.577</v>
       </c>
     </row>
     <row r="232">
@@ -3731,10 +3731,10 @@
         <v>46454.04166666666</v>
       </c>
       <c r="C232" s="2" t="n">
-        <v>4.906131744384766</v>
+        <v>5.111</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>96.41255256316329</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="233">
@@ -3745,10 +3745,10 @@
         <v>46454.125</v>
       </c>
       <c r="C233" s="2" t="n">
-        <v>4.877048492431641</v>
+        <v>5.293</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>96.36442097960349</v>
+        <v>97.60899999999999</v>
       </c>
     </row>
     <row r="234">
@@ -3759,10 +3759,10 @@
         <v>46454.16666666666</v>
       </c>
       <c r="C234" s="2" t="n">
-        <v>4.857639312744141</v>
+        <v>5.234</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>96.28875181790866</v>
+        <v>97.47199999999999</v>
       </c>
     </row>
     <row r="235">
@@ -3773,10 +3773,10 @@
         <v>46454.20833333334</v>
       </c>
       <c r="C235" s="2" t="n">
-        <v>4.854404449462891</v>
+        <v>5.499</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>96.265258081835</v>
+        <v>97.545</v>
       </c>
     </row>
     <row r="236">
@@ -3787,10 +3787,10 @@
         <v>46454.25</v>
       </c>
       <c r="C236" s="2" t="n">
-        <v>4.849552154541016</v>
+        <v>5.808</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>96.23700379022894</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="237">
@@ -3801,10 +3801,10 @@
         <v>46454.29166666666</v>
       </c>
       <c r="C237" s="2" t="n">
-        <v>4.843082427978516</v>
+        <v>5.582</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>96.22266952080813</v>
+        <v>97.256</v>
       </c>
     </row>
     <row r="238">
@@ -3815,10 +3815,10 @@
         <v>46454.33333333334</v>
       </c>
       <c r="C238" s="2" t="n">
-        <v>4.822055816650391</v>
+        <v>5.246</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>96.23094789016629</v>
+        <v>97.45399999999999</v>
       </c>
     </row>
     <row r="239">
@@ -3829,10 +3829,10 @@
         <v>46454.375</v>
       </c>
       <c r="C239" s="2" t="n">
-        <v>4.818820953369141</v>
+        <v>5.461</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>96.23078350634265</v>
+        <v>97.498</v>
       </c>
     </row>
     <row r="240">
@@ -3843,10 +3843,10 @@
         <v>46454.41666666666</v>
       </c>
       <c r="C240" s="2" t="n">
-        <v>4.846317291259766</v>
+        <v>5.3</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>96.21817855474646</v>
+        <v>97.43000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -3857,10 +3857,10 @@
         <v>46454.45833333334</v>
       </c>
       <c r="C241" s="2" t="n">
-        <v>4.907749176025391</v>
+        <v>5.185</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>96.225930895869</v>
+        <v>97.414</v>
       </c>
     </row>
     <row r="242">
@@ -3871,10 +3871,10 @@
         <v>46454.5</v>
       </c>
       <c r="C242" s="2" t="n">
-        <v>4.994937896728516</v>
+        <v>5.564</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>96.12762936933635</v>
+        <v>97.16200000000001</v>
       </c>
     </row>
     <row r="243">
@@ -3885,10 +3885,10 @@
         <v>46454.54166666666</v>
       </c>
       <c r="C243" s="2" t="n">
-        <v>5.064304351806641</v>
+        <v>5.493</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>96.11709565391794</v>
+        <v>97.303</v>
       </c>
     </row>
     <row r="244">
@@ -3899,10 +3899,10 @@
         <v>46454.58333333334</v>
       </c>
       <c r="C244" s="2" t="n">
-        <v>5.172275543212891</v>
+        <v>5.805</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>96.09449616584484</v>
+        <v>97.166</v>
       </c>
     </row>
     <row r="245">
@@ -3913,10 +3913,10 @@
         <v>46454.625</v>
       </c>
       <c r="C245" s="2" t="n">
-        <v>5.233463287353516</v>
+        <v>5.684</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>96.07421120200851</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="246">
@@ -3927,10 +3927,10 @@
         <v>46454.66666666666</v>
       </c>
       <c r="C246" s="2" t="n">
-        <v>5.251163482666016</v>
+        <v>5.647</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>96.14978173340916</v>
+        <v>97.34399999999999</v>
       </c>
     </row>
     <row r="247">
@@ -3941,10 +3941,10 @@
         <v>46454.70833333334</v>
       </c>
       <c r="C247" s="2" t="n">
-        <v>5.204502105712891</v>
+        <v>5.738</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>96.1521225590577</v>
+        <v>97.438</v>
       </c>
     </row>
     <row r="248">
@@ -3955,10 +3955,10 @@
         <v>46454.75</v>
       </c>
       <c r="C248" s="2" t="n">
-        <v>5.115909576416016</v>
+        <v>5.61</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>96.14302227058137</v>
+        <v>97.322</v>
       </c>
     </row>
     <row r="249">
@@ -3969,10 +3969,10 @@
         <v>46454.79166666666</v>
       </c>
       <c r="C249" s="2" t="n">
-        <v>4.970737457275391</v>
+        <v>5.549</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>96.1310748542797</v>
+        <v>97.20099999999999</v>
       </c>
     </row>
     <row r="250">
@@ -3983,10 +3983,10 @@
         <v>46454.83333333334</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>4.797794342041016</v>
+        <v>5.431</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>96.10370823532125</v>
+        <v>97.217</v>
       </c>
     </row>
     <row r="251">
@@ -3997,10 +3997,10 @@
         <v>46454.875</v>
       </c>
       <c r="C251" s="2" t="n">
-        <v>4.617984771728516</v>
+        <v>5.161</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>96.10863317467729</v>
+        <v>97.15900000000001</v>
       </c>
     </row>
     <row r="252">
@@ -4011,10 +4011,10 @@
         <v>46454.91666666666</v>
       </c>
       <c r="C252" s="2" t="n">
-        <v>4.444278717041016</v>
+        <v>4.882</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>96.1604929833571</v>
+        <v>97.33199999999999</v>
       </c>
     </row>
     <row r="253">
@@ -4025,10 +4025,10 @@
         <v>46454.95833333334</v>
       </c>
       <c r="C253" s="2" t="n">
-        <v>4.250614166259766</v>
+        <v>4.736</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>96.17864095748621</v>
+        <v>97.455</v>
       </c>
     </row>
     <row r="254">
@@ -4039,10 +4039,10 @@
         <v>46455</v>
       </c>
       <c r="C254" s="2" t="n">
-        <v>4.076084136962891</v>
+        <v>4.714</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>96.17438012877763</v>
+        <v>97.301</v>
       </c>
     </row>
     <row r="255">
@@ -4053,10 +4053,10 @@
         <v>46455.04166666666</v>
       </c>
       <c r="C255" s="2" t="n">
-        <v>3.917514562606812</v>
+        <v>4.392</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>96.14291706493424</v>
+        <v>97.351</v>
       </c>
     </row>
     <row r="256">
@@ -4067,10 +4067,10 @@
         <v>46455.08333333334</v>
       </c>
       <c r="C256" s="2" t="n">
-        <v>3.770084142684937</v>
+        <v>4.46</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>96.15400311000006</v>
+        <v>97.36499999999999</v>
       </c>
     </row>
     <row r="257">
@@ -4081,10 +4081,10 @@
         <v>46455.125</v>
       </c>
       <c r="C257" s="2" t="n">
-        <v>3.655185461044312</v>
+        <v>4.315</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>96.12474936474629</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="258">
@@ -4095,10 +4095,10 @@
         <v>46455.16666666666</v>
       </c>
       <c r="C258" s="2" t="n">
-        <v>3.536838293075562</v>
+        <v>4.166</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>96.09529835890417</v>
+        <v>97.23699999999999</v>
       </c>
     </row>
     <row r="259">
@@ -4109,10 +4109,10 @@
         <v>46455.20833333334</v>
       </c>
       <c r="C259" s="2" t="n">
-        <v>3.438052892684937</v>
+        <v>3.879</v>
       </c>
       <c r="D259" s="3" t="n">
-        <v>96.11351208656274</v>
+        <v>97.324</v>
       </c>
     </row>
     <row r="260">
@@ -4123,10 +4123,10 @@
         <v>46455.25</v>
       </c>
       <c r="C260" s="2" t="n">
-        <v>3.350711584091187</v>
+        <v>3.452</v>
       </c>
       <c r="D260" s="3" t="n">
-        <v>96.16495764800698</v>
+        <v>97.411</v>
       </c>
     </row>
     <row r="261">
@@ -4137,10 +4137,10 @@
         <v>46455.29166666666</v>
       </c>
       <c r="C261" s="2" t="n">
-        <v>3.276431798934937</v>
+        <v>3.857</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>96.21706732009869</v>
+        <v>97.39700000000001</v>
       </c>
     </row>
     <row r="262">
@@ -4151,10 +4151,10 @@
         <v>46455.33333333334</v>
       </c>
       <c r="C262" s="2" t="n">
-        <v>3.226901769638062</v>
+        <v>4.008</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>96.24246790852651</v>
+        <v>97.408</v>
       </c>
     </row>
     <row r="263">
@@ -4165,10 +4165,10 @@
         <v>46455.375</v>
       </c>
       <c r="C263" s="2" t="n">
-        <v>3.193851232528687</v>
+        <v>3.769</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>96.27340494413427</v>
+        <v>97.249</v>
       </c>
     </row>
     <row r="264">
@@ -4179,10 +4179,10 @@
         <v>46455.41666666666</v>
       </c>
       <c r="C264" s="2" t="n">
-        <v>3.167392492294312</v>
+        <v>4.061</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>96.30467732274225</v>
+        <v>97.529</v>
       </c>
     </row>
     <row r="265">
@@ -4193,10 +4193,10 @@
         <v>46455.45833333334</v>
       </c>
       <c r="C265" s="2" t="n">
-        <v>3.150851964950562</v>
+        <v>3.636</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>96.30381595150641</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="266">
@@ -4207,10 +4207,10 @@
         <v>46455.5</v>
       </c>
       <c r="C266" s="2" t="n">
-        <v>3.155826330184937</v>
+        <v>3.92</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>96.31340939145365</v>
+        <v>97.47799999999999</v>
       </c>
     </row>
     <row r="267">
@@ -4221,10 +4221,10 @@
         <v>46455.54166666666</v>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3.203769445419312</v>
+        <v>3.821</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>96.28791674808461</v>
+        <v>97.63200000000001</v>
       </c>
     </row>
     <row r="268">
@@ -4235,10 +4235,10 @@
         <v>46455.58333333334</v>
       </c>
       <c r="C268" s="2" t="n">
-        <v>3.311099767684937</v>
+        <v>3.845</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>96.25619724547634</v>
+        <v>97.387</v>
       </c>
     </row>
     <row r="269">
@@ -4249,10 +4249,10 @@
         <v>46455.625</v>
       </c>
       <c r="C269" s="2" t="n">
-        <v>3.413364171981812</v>
+        <v>3.977</v>
       </c>
       <c r="D269" s="3" t="n">
-        <v>96.23818735375909</v>
+        <v>97.42100000000001</v>
       </c>
     </row>
     <row r="270">
@@ -4263,10 +4263,10 @@
         <v>46455.66666666666</v>
       </c>
       <c r="C270" s="2" t="n">
-        <v>3.503940343856812</v>
+        <v>4.33</v>
       </c>
       <c r="D270" s="3" t="n">
-        <v>96.21022895303555</v>
+        <v>97.477</v>
       </c>
     </row>
     <row r="271">
@@ -4277,10 +4277,10 @@
         <v>46455.70833333334</v>
       </c>
       <c r="C271" s="2" t="n">
-        <v>3.546725988388062</v>
+        <v>4.181</v>
       </c>
       <c r="D271" s="3" t="n">
-        <v>96.18912207008105</v>
+        <v>97.274</v>
       </c>
     </row>
     <row r="272">
@@ -4291,10 +4291,10 @@
         <v>46455.75</v>
       </c>
       <c r="C272" s="2" t="n">
-        <v>3.558200597763062</v>
+        <v>3.997</v>
       </c>
       <c r="D272" s="3" t="n">
-        <v>96.14772364793727</v>
+        <v>97.26000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -4305,10 +4305,10 @@
         <v>46455.79166666666</v>
       </c>
       <c r="C273" s="2" t="n">
-        <v>3.498996496200562</v>
+        <v>4.193</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>96.12133018121473</v>
+        <v>97.158</v>
       </c>
     </row>
     <row r="274">
@@ -4319,10 +4319,10 @@
         <v>46455.83333333334</v>
       </c>
       <c r="C274" s="2" t="n">
-        <v>3.192203283309937</v>
+        <v>3.679</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>96.14270007828705</v>
+        <v>97.346</v>
       </c>
     </row>
     <row r="275">
@@ -4333,10 +4333,10 @@
         <v>46455.875</v>
       </c>
       <c r="C275" s="2" t="n">
-        <v>3.135959386825562</v>
+        <v>3.655</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>96.16309682312345</v>
+        <v>97.264</v>
       </c>
     </row>
     <row r="276">
@@ -4347,10 +4347,10 @@
         <v>46455.91666666666</v>
       </c>
       <c r="C276" s="2" t="n">
-        <v>3.076389074325562</v>
+        <v>3.661</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>96.1972952337921</v>
+        <v>97.306</v>
       </c>
     </row>
     <row r="277">
@@ -4361,10 +4361,10 @@
         <v>46455.95833333334</v>
       </c>
       <c r="C277" s="2" t="n">
-        <v>3.034976720809937</v>
+        <v>3.547</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>96.2044623685025</v>
+        <v>97.32599999999999</v>
       </c>
     </row>
     <row r="278">
@@ -4375,10 +4375,10 @@
         <v>46456</v>
       </c>
       <c r="C278" s="2" t="n">
-        <v>2.967014074325562</v>
+        <v>3.413</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>96.177582325662</v>
+        <v>97.25700000000001</v>
       </c>
     </row>
     <row r="279">
@@ -4389,10 +4389,10 @@
         <v>46456.04166666666</v>
       </c>
       <c r="C279" s="2" t="n">
-        <v>2.877414464950562</v>
+        <v>3.365</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>96.15422667200021</v>
+        <v>97.485</v>
       </c>
     </row>
     <row r="280">
@@ -4403,10 +4403,10 @@
         <v>46456.08333333334</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>2.814304113388062</v>
+        <v>3.417</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>96.16490504518342</v>
+        <v>97.358</v>
       </c>
     </row>
     <row r="281">
@@ -4417,10 +4417,10 @@
         <v>46456.125</v>
       </c>
       <c r="C281" s="2" t="n">
-        <v>2.732822179794312</v>
+        <v>3.413</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>96.16994176553953</v>
+        <v>97.36199999999999</v>
       </c>
     </row>
     <row r="282">
@@ -4431,10 +4431,10 @@
         <v>46456.16666666666</v>
       </c>
       <c r="C282" s="2" t="n">
-        <v>2.644565343856812</v>
+        <v>3.249</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>96.1466387147013</v>
+        <v>97.312</v>
       </c>
     </row>
     <row r="283">
@@ -4445,10 +4445,10 @@
         <v>46456.20833333334</v>
       </c>
       <c r="C283" s="2" t="n">
-        <v>2.567874670028687</v>
+        <v>2.802</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>96.17056642406934</v>
+        <v>97.223</v>
       </c>
     </row>
     <row r="284">
@@ -4459,10 +4459,10 @@
         <v>46456.25</v>
       </c>
       <c r="C284" s="2" t="n">
-        <v>2.519504308700562</v>
+        <v>2.754</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>96.21465416556777</v>
+        <v>97.32899999999999</v>
       </c>
     </row>
     <row r="285">
@@ -4473,10 +4473,10 @@
         <v>46456.29166666666</v>
       </c>
       <c r="C285" s="2" t="n">
-        <v>2.504459142684937</v>
+        <v>3.217</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>96.27447672666436</v>
+        <v>97.358</v>
       </c>
     </row>
     <row r="286">
@@ -4487,10 +4487,10 @@
         <v>46456.33333333334</v>
       </c>
       <c r="C286" s="2" t="n">
-        <v>2.471072912216187</v>
+        <v>2.771</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>96.35200013788977</v>
+        <v>97.551</v>
       </c>
     </row>
     <row r="287">
@@ -4501,10 +4501,10 @@
         <v>46456.375</v>
       </c>
       <c r="C287" s="2" t="n">
-        <v>2.476077795028687</v>
+        <v>3.048</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>96.44553453353706</v>
+        <v>97.521</v>
       </c>
     </row>
     <row r="288">
@@ -4515,10 +4515,10 @@
         <v>46456.41666666666</v>
       </c>
       <c r="C288" s="2" t="n">
-        <v>2.522830724716187</v>
+        <v>3.242</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>96.5133132716975</v>
+        <v>97.723</v>
       </c>
     </row>
     <row r="289">
@@ -4529,10 +4529,10 @@
         <v>46456.45833333334</v>
       </c>
       <c r="C289" s="2" t="n">
-        <v>2.559543371200562</v>
+        <v>3.236</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>96.51059107557813</v>
+        <v>97.59099999999999</v>
       </c>
     </row>
     <row r="290">
@@ -4543,10 +4543,10 @@
         <v>46456.5</v>
       </c>
       <c r="C290" s="2" t="n">
-        <v>2.604556798934937</v>
+        <v>3.141</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>96.5223083545267</v>
+        <v>97.622</v>
       </c>
     </row>
     <row r="291">
@@ -4557,10 +4557,10 @@
         <v>46456.54166666666</v>
       </c>
       <c r="C291" s="2" t="n">
-        <v>2.642886877059937</v>
+        <v>3.204</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>96.49168036050737</v>
+        <v>97.417</v>
       </c>
     </row>
     <row r="292">
@@ -4571,10 +4571,10 @@
         <v>46456.58333333334</v>
       </c>
       <c r="C292" s="2" t="n">
-        <v>2.752780675888062</v>
+        <v>3.215</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>96.48350062144338</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="293">
@@ -4585,10 +4585,10 @@
         <v>46456.625</v>
       </c>
       <c r="C293" s="2" t="n">
-        <v>2.894016027450562</v>
+        <v>3.641</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>96.49559269550984</v>
+        <v>97.545</v>
       </c>
     </row>
     <row r="294">
@@ -4599,10 +4599,10 @@
         <v>46456.66666666666</v>
       </c>
       <c r="C294" s="2" t="n">
-        <v>3.018405675888062</v>
+        <v>3.586</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>96.46947539361099</v>
+        <v>97.515</v>
       </c>
     </row>
     <row r="295">
@@ -4613,10 +4613,10 @@
         <v>46456.70833333334</v>
       </c>
       <c r="C295" s="2" t="n">
-        <v>3.129337072372437</v>
+        <v>3.765</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>96.49394885727351</v>
+        <v>97.79300000000001</v>
       </c>
     </row>
     <row r="296">
@@ -4627,10 +4627,10 @@
         <v>46456.75</v>
       </c>
       <c r="C296" s="2" t="n">
-        <v>3.220279455184937</v>
+        <v>3.759</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>96.51736368911182</v>
+        <v>97.599</v>
       </c>
     </row>
     <row r="297">
@@ -4641,10 +4641,10 @@
         <v>46456.79166666666</v>
       </c>
       <c r="C297" s="2" t="n">
-        <v>3.243411779403687</v>
+        <v>3.538</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>96.53722783035965</v>
+        <v>97.60599999999999</v>
       </c>
     </row>
     <row r="298">
@@ -4655,10 +4655,10 @@
         <v>46456.83333333334</v>
       </c>
       <c r="C298" s="2" t="n">
-        <v>3.225253820419312</v>
+        <v>3.629</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>96.5736158335591</v>
+        <v>97.699</v>
       </c>
     </row>
     <row r="299">
@@ -4669,10 +4669,10 @@
         <v>46456.875</v>
       </c>
       <c r="C299" s="2" t="n">
-        <v>3.183933019638062</v>
+        <v>3.861</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>96.56677746649595</v>
+        <v>97.676</v>
       </c>
     </row>
     <row r="300">
@@ -4683,10 +4683,10 @@
         <v>46456.91666666666</v>
       </c>
       <c r="C300" s="2" t="n">
-        <v>3.111148595809937</v>
+        <v>3.557</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>96.59562353986711</v>
+        <v>97.806</v>
       </c>
     </row>
     <row r="301">
@@ -4697,10 +4697,10 @@
         <v>46456.95833333334</v>
       </c>
       <c r="C301" s="2" t="n">
-        <v>3.056522130966187</v>
+        <v>3.635</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>96.61609261358592</v>
+        <v>97.869</v>
       </c>
     </row>
     <row r="302">
@@ -4711,10 +4711,10 @@
         <v>46457</v>
       </c>
       <c r="C302" s="2" t="n">
-        <v>3.003513097763062</v>
+        <v>3.797</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>96.60398081346062</v>
+        <v>97.774</v>
       </c>
     </row>
     <row r="303">
@@ -4725,10 +4725,10 @@
         <v>46457.04166666666</v>
       </c>
       <c r="C303" s="2" t="n">
-        <v>2.942142248153687</v>
+        <v>3.512</v>
       </c>
       <c r="D303" s="3" t="n">
-        <v>96.59607723922034</v>
+        <v>97.727</v>
       </c>
     </row>
     <row r="304">
@@ -4739,10 +4739,10 @@
         <v>46457.08333333334</v>
       </c>
       <c r="C304" s="2" t="n">
-        <v>2.879092931747437</v>
+        <v>3.3</v>
       </c>
       <c r="D304" s="3" t="n">
-        <v>96.61142411299473</v>
+        <v>97.687</v>
       </c>
     </row>
     <row r="305">
@@ -4753,10 +4753,10 @@
         <v>46457.125</v>
       </c>
       <c r="C305" s="2" t="n">
-        <v>2.844211339950562</v>
+        <v>3.444</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>96.6189200153524</v>
+        <v>97.67100000000001</v>
       </c>
     </row>
     <row r="306">
@@ -4767,10 +4767,10 @@
         <v>46457.16666666666</v>
       </c>
       <c r="C306" s="2" t="n">
-        <v>2.804324865341187</v>
+        <v>3.65</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>96.6168159024099</v>
+        <v>97.874</v>
       </c>
     </row>
     <row r="307">
@@ -4781,10 +4781,10 @@
         <v>46457.20833333334</v>
       </c>
       <c r="C307" s="2" t="n">
-        <v>2.761081457138062</v>
+        <v>3.152</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>96.6238646807673</v>
+        <v>97.89700000000001</v>
       </c>
     </row>
     <row r="308">
@@ -4795,10 +4795,10 @@
         <v>46457.25</v>
       </c>
       <c r="C308" s="2" t="n">
-        <v>2.729465246200562</v>
+        <v>3.147</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>96.5988717642221</v>
+        <v>97.80200000000001</v>
       </c>
     </row>
     <row r="309">
@@ -4809,10 +4809,10 @@
         <v>46457.29166666666</v>
       </c>
       <c r="C309" s="2" t="n">
-        <v>2.701205968856812</v>
+        <v>3.252</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>96.60670300957999</v>
+        <v>97.843</v>
       </c>
     </row>
     <row r="310">
@@ -4823,10 +4823,10 @@
         <v>46457.33333333334</v>
       </c>
       <c r="C310" s="2" t="n">
-        <v>2.626254796981812</v>
+        <v>3.11</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>96.57942187020983</v>
+        <v>97.735</v>
       </c>
     </row>
     <row r="311">
@@ -4837,10 +4837,10 @@
         <v>46457.375</v>
       </c>
       <c r="C311" s="2" t="n">
-        <v>2.511173009872437</v>
+        <v>2.9</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>96.5919807943354</v>
+        <v>97.782</v>
       </c>
     </row>
     <row r="312">
@@ -4851,10 +4851,10 @@
         <v>46457.41666666666</v>
       </c>
       <c r="C312" s="2" t="n">
-        <v>2.441013097763062</v>
+        <v>3</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>96.56027444243303</v>
+        <v>97.57299999999999</v>
       </c>
     </row>
     <row r="313">
@@ -4865,10 +4865,10 @@
         <v>46457.45833333334</v>
       </c>
       <c r="C313" s="2" t="n">
-        <v>2.355716466903687</v>
+        <v>3.052</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>96.50443654522131</v>
+        <v>97.621</v>
       </c>
     </row>
     <row r="314">
@@ -4879,10 +4879,10 @@
         <v>46457.5</v>
       </c>
       <c r="C314" s="2" t="n">
-        <v>2.263644933700562</v>
+        <v>2.957</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>96.40160460050932</v>
+        <v>97.614</v>
       </c>
     </row>
     <row r="315">
@@ -4893,10 +4893,10 @@
         <v>46457.54166666666</v>
       </c>
       <c r="C315" s="2" t="n">
-        <v>2.037082433700562</v>
+        <v>2.611</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>96.3941744516811</v>
+        <v>97.595</v>
       </c>
     </row>
   </sheetData>
